--- a/reports/hackathon-2026-07-26/hackathon_cost_breakdown.xlsx
+++ b/reports/hackathon-2026-07-26/hackathon_cost_breakdown.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Per-user summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="User × model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Per-turn detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Per-project" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Model totals" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-user summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User × model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-turn detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-project" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model totals" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/reports/hackathon-2026-07-26/hackathon_cost_breakdown.xlsx
+++ b/reports/hackathon-2026-07-26/hackathon_cost_breakdown.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>claude-opus-4-6, (blank), claude-sonnet-4-6</t>
+          <t>claude-opus-4-6, claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6, (blank)</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6, (blank)</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6, claude-opus-4-6, (blank)</t>
+          <t>claude-sonnet-4-6, claude-opus-4-6</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6, (blank)</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -2185,11 +2185,9 @@
         <v>8.9</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>65.56</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>20.75</v>
-      </c>
+        <v>86.31</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
@@ -2210,10 +2208,10 @@
         <v>1.01</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>26.16</v>
+        <v>26.67</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2.51</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
@@ -2232,12 +2230,10 @@
         <v>26.7</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>19.59</v>
+        <v>26.7</v>
       </c>
       <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n">
-        <v>7.1</v>
-      </c>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
@@ -2278,12 +2274,10 @@
         <v>15.21</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11.61</v>
+        <v>15.21</v>
       </c>
       <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
@@ -2301,14 +2295,12 @@
         <v>14.1</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>10.89</v>
+        <v>12.45</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1.64</v>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>1.56</v>
-      </c>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
@@ -2474,11 +2466,11 @@
       <c r="C15" s="2" t="n">
         <v>7.38</v>
       </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>7.38</v>
+      </c>
       <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n">
-        <v>7.38</v>
-      </c>
+      <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
@@ -2769,12 +2761,10 @@
         <v>2.74</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1.38</v>
+        <v>2.74</v>
       </c>
       <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n">
-        <v>1.37</v>
-      </c>
+      <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="n"/>
@@ -3130,16 +3120,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G231"/>
+  <dimension ref="A1:H231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3165,15 +3156,20 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Model source</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Cost USD</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Key type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Project ID</t>
         </is>
@@ -3200,15 +3196,20 @@
           <t>gpt-5.4</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>1.7386</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>prj_4a420277e75948f8a54a6326131e7ebc</t>
         </is>
@@ -3235,15 +3236,20 @@
           <t>gpt-5.4</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>1.4394</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>prj_4a420277e75948f8a54a6326131e7ebc</t>
         </is>
@@ -3270,15 +3276,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>1.827</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>prj_dafde1251b6940458b46b6227142a03f</t>
         </is>
@@ -3305,15 +3316,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>0.0717</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>prj_e0a8e92dbfa14efebfe76d073967ae58</t>
         </is>
@@ -3340,15 +3356,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>0.0337</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>prj_e0a8e92dbfa14efebfe76d073967ae58</t>
         </is>
@@ -3375,15 +3396,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>0.0375</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>prj_e0a8e92dbfa14efebfe76d073967ae58</t>
         </is>
@@ -3410,15 +3436,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
         <v>0.0336</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>prj_e0a8e92dbfa14efebfe76d073967ae58</t>
         </is>
@@ -3445,15 +3476,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>0.0306</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>prj_8b6bccf2526f4b59aa02df3d39b1bc76</t>
         </is>
@@ -3480,15 +3516,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>0.1069</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>prj_465443b9ab494e4b9cfc467954362ac0</t>
         </is>
@@ -3515,15 +3556,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>0.0478</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>prj_465443b9ab494e4b9cfc467954362ac0</t>
         </is>
@@ -3550,15 +3596,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>2.8277</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>prj_794da3117b7b446bb859f76773f4882a</t>
         </is>
@@ -3585,15 +3636,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>0.0814</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>prj_465443b9ab494e4b9cfc467954362ac0</t>
         </is>
@@ -3620,15 +3676,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
         <v>1.4296</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>prj_dafde1251b6940458b46b6227142a03f</t>
         </is>
@@ -3655,15 +3716,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>1.2804</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>prj_794da3117b7b446bb859f76773f4882a</t>
         </is>
@@ -3690,15 +3756,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>0.9426</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>prj_dafde1251b6940458b46b6227142a03f</t>
         </is>
@@ -3725,15 +3796,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
         <v>1.3852</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>prj_4cb223a06d044e3884571a1a9db05c15</t>
         </is>
@@ -3760,15 +3836,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
         <v>3.5575</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>prj_07924aa5d8844a4c92ec1db23476ff4a</t>
         </is>
@@ -3795,15 +3876,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
         <v>4.2283</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>prj_e221843d682c48b1a60cff3283d0d81c</t>
         </is>
@@ -3830,15 +3916,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
         <v>0.121</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>prj_51a8b847823248a093dcdbf1067a9a6b</t>
         </is>
@@ -3865,15 +3956,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
         <v>1.3989</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>prj_07924aa5d8844a4c92ec1db23476ff4a</t>
         </is>
@@ -3900,15 +3996,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
         <v>5.0807</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>prj_154ea02e80f04b71877b98956e565c12</t>
         </is>
@@ -3935,15 +4036,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
         <v>2.2651</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>prj_b88f4c0b585642c899688ce48603ea48</t>
         </is>
@@ -3970,15 +4076,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
         <v>1.9518</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>prj_3c602ac0e7c845da83a5c97fa9563637</t>
         </is>
@@ -4005,15 +4116,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
         <v>3.6805</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>prj_715a659716294948bf46a6425577322c</t>
         </is>
@@ -4040,15 +4156,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
         <v>0.3627</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>prj_715a659716294948bf46a6425577322c</t>
         </is>
@@ -4075,15 +4196,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
         <v>0.0253</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>prj_4620f251f9ab4774b9aa1a1d2f70b200</t>
         </is>
@@ -4110,15 +4236,20 @@
           <t>claude-opus-4-5-20251101</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
         <v>0.3051</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>byok</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>prj_3dfb58dc3ca8426e942cc2306d8b7b85</t>
         </is>
@@ -4145,15 +4276,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
         <v>3.4091</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>prj_c650bb9fe85c46129b6250e1e9103c2e</t>
         </is>
@@ -4177,18 +4313,23 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
         <v>1.7616</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>prj_07924aa5d8844a4c92ec1db23476ff4a</t>
         </is>
@@ -4215,15 +4356,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
         <v>3.1954</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>prj_154ea02e80f04b71877b98956e565c12</t>
         </is>
@@ -4250,15 +4396,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
         <v>0.871</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>prj_3c602ac0e7c845da83a5c97fa9563637</t>
         </is>
@@ -4285,15 +4436,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
         <v>2.7536</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>prj_97639f12bbf345a09ee342fede643ac6</t>
         </is>
@@ -4320,15 +4476,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
         <v>0.0905</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -4352,18 +4513,23 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="n">
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
         <v>1.8367</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>prj_07924aa5d8844a4c92ec1db23476ff4a</t>
         </is>
@@ -4390,15 +4556,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
         <v>0.2648</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>prj_4f409ce952ed458ebf2627aa06c44fad</t>
         </is>
@@ -4425,15 +4596,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
         <v>0.068</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -4460,15 +4636,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
         <v>0.0371</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -4495,15 +4676,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
         <v>0.2355</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G39" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>prj_07924aa5d8844a4c92ec1db23476ff4a</t>
         </is>
@@ -4530,15 +4716,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
         <v>0.6019</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>prj_4cb223a06d044e3884571a1a9db05c15</t>
         </is>
@@ -4565,15 +4756,20 @@
           <t>gpt-5.2</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
         <v>0.2298</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>prj_3dfb58dc3ca8426e942cc2306d8b7b85</t>
         </is>
@@ -4600,15 +4796,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
         <v>0.2058</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -4635,15 +4836,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
         <v>0.0426</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -4670,15 +4876,20 @@
           <t>gpt-5.2</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
         <v>0.0756</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>prj_3dfb58dc3ca8426e942cc2306d8b7b85</t>
         </is>
@@ -4705,15 +4916,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
         <v>0.2131</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -4740,15 +4956,20 @@
           <t>gpt-5.2</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
         <v>0.0701</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>prj_3dfb58dc3ca8426e942cc2306d8b7b85</t>
         </is>
@@ -4775,15 +4996,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
         <v>0.1297</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -4810,15 +5036,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
         <v>0.8434</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>prj_07924aa5d8844a4c92ec1db23476ff4a</t>
         </is>
@@ -4845,15 +5076,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -4880,15 +5116,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
         <v>0.2485</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>prj_07924aa5d8844a4c92ec1db23476ff4a</t>
         </is>
@@ -4915,15 +5156,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
         <v>0.7811</v>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>prj_3c602ac0e7c845da83a5c97fa9563637</t>
         </is>
@@ -4950,15 +5196,20 @@
           <t>gpt-5.2</t>
         </is>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
         <v>0.1559</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>prj_4cb223a06d044e3884571a1a9db05c15</t>
         </is>
@@ -4985,15 +5236,20 @@
           <t>gpt-5.2</t>
         </is>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
         <v>0.0301</v>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G53" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>prj_4cb223a06d044e3884571a1a9db05c15</t>
         </is>
@@ -5020,15 +5276,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
         <v>2.9447</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G54" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>prj_4f409ce952ed458ebf2627aa06c44fad</t>
         </is>
@@ -5055,15 +5316,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
         <v>0.4878</v>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5090,15 +5356,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
         <v>0.0545</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G56" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5125,15 +5396,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n">
         <v>0.0555</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G57" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5160,15 +5436,20 @@
           <t>gpt-5.2</t>
         </is>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n">
         <v>0.2079</v>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>prj_4cb223a06d044e3884571a1a9db05c15</t>
         </is>
@@ -5195,15 +5476,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n">
         <v>0.7586000000000001</v>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G59" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>prj_4f409ce952ed458ebf2627aa06c44fad</t>
         </is>
@@ -5230,15 +5516,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
         <v>0.0561</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G60" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5265,15 +5556,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n">
         <v>0.4002</v>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G61" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>prj_3c602ac0e7c845da83a5c97fa9563637</t>
         </is>
@@ -5300,15 +5596,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
         <v>2.1127</v>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G62" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
@@ -5335,15 +5636,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n">
         <v>1.2016</v>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G63" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>prj_07924aa5d8844a4c92ec1db23476ff4a</t>
         </is>
@@ -5370,15 +5676,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
         <v>0.1331</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
@@ -5405,15 +5716,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
         <v>0.1883</v>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G65" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
         <is>
           <t>prj_07924aa5d8844a4c92ec1db23476ff4a</t>
         </is>
@@ -5440,15 +5756,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
         <v>2.5952</v>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G66" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5475,15 +5796,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
         <v>0.1695</v>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G67" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5510,15 +5836,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
         <v>0.0253</v>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
         <is>
           <t>prj_3f1220f275a5465f91ddb4c885d651ac</t>
         </is>
@@ -5545,15 +5876,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
         <v>0.06900000000000001</v>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G69" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5580,15 +5916,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
         <v>0.0723</v>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5615,15 +5956,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
         <v>0.4328</v>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G71" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
         <is>
           <t>prj_b88f4c0b585642c899688ce48603ea48</t>
         </is>
@@ -5650,15 +5996,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
         <v>0.9977</v>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G72" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t>prj_07924aa5d8844a4c92ec1db23476ff4a</t>
         </is>
@@ -5685,15 +6036,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
         <v>0.1318</v>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G73" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5720,15 +6076,20 @@
           <t>(blank)</t>
         </is>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
         <v>2.3367</v>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G74" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t>3a4b96ec-339b-4a92-833f-94048883eb44</t>
         </is>
@@ -5755,15 +6116,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
         <v>0.413</v>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5790,15 +6156,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
         <v>0.3652</v>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G76" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5825,15 +6196,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
         <v>7.337</v>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t>prj_ce4dd6df91864d219f2baa8910a1d9ea</t>
         </is>
@@ -5860,15 +6236,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
         <v>0.2614</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G78" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5895,15 +6276,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
         <v>1.442</v>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G79" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
         <is>
           <t>prj_07924aa5d8844a4c92ec1db23476ff4a</t>
         </is>
@@ -5930,15 +6316,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
         <v>0.0794</v>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -5965,15 +6356,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E81" s="2" t="n">
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
         <v>0.0804</v>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G81" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -6000,15 +6396,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
         <v>2.3234</v>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
@@ -6035,15 +6436,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E83" s="2" t="n">
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
         <v>0.6802</v>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -6070,15 +6476,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E84" s="2" t="n">
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
         <v>0.0935</v>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G84" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
         <is>
           <t>34dbf079-fc90-41f4-968e-036f650caa81</t>
         </is>
@@ -6105,15 +6516,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E85" s="2" t="n">
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
         <v>0.1925</v>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G85" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
@@ -6140,15 +6556,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E86" s="2" t="n">
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
         <v>0.5436</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G86" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
         <is>
           <t>prj_b88f4c0b585642c899688ce48603ea48</t>
         </is>
@@ -6175,15 +6596,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E87" s="2" t="n">
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
         <v>0.0863</v>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G87" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -6210,15 +6636,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E88" s="2" t="n">
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
         <v>0.08649999999999999</v>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G88" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -6245,15 +6676,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E89" s="2" t="n">
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
         <v>3.4957</v>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G89" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>fa325ad8-92a1-460b-bebc-6e41d0744990</t>
         </is>
@@ -6280,15 +6716,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E90" s="2" t="n">
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
         <v>0.08890000000000001</v>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G90" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -6315,15 +6756,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E91" s="2" t="n">
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
         <v>0.117</v>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G91" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
         <is>
           <t>prj_b88f4c0b585642c899688ce48603ea48</t>
         </is>
@@ -6350,15 +6796,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E92" s="2" t="n">
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
         <v>0.1704</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G92" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -6385,15 +6836,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E93" s="2" t="n">
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
         <v>5.8299</v>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G93" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
         <is>
           <t>prj_826a6397e8994cdf9b1284c5daf5d5ac</t>
         </is>
@@ -6420,15 +6876,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E94" s="2" t="n">
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
         <v>0.248</v>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G94" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -6455,15 +6916,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E95" s="2" t="n">
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G95" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
         <is>
           <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
@@ -6490,15 +6956,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E96" s="2" t="n">
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
         <v>0.2192</v>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G96" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
         <is>
           <t>prj_b88f4c0b585642c899688ce48603ea48</t>
         </is>
@@ -6525,15 +6996,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E97" s="2" t="n">
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
         <v>1.5622</v>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G97" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
         <is>
           <t>fa325ad8-92a1-460b-bebc-6e41d0744990</t>
         </is>
@@ -6560,15 +7036,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E98" s="2" t="n">
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
         <v>0.1852</v>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G98" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
         <is>
           <t>prj_f66b714e163345618972deabd55a5407</t>
         </is>
@@ -6595,15 +7076,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E99" s="2" t="n">
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
         <v>0.4986</v>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G99" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -6630,15 +7116,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E100" s="2" t="n">
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
         <v>0.1731</v>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G100" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
         <is>
           <t>prj_b88f4c0b585642c899688ce48603ea48</t>
         </is>
@@ -6665,15 +7156,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E101" s="2" t="n">
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
         <v>0.3501</v>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G101" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -6700,15 +7196,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E102" s="2" t="n">
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
         <v>0.6983</v>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G102" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
         <is>
           <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
@@ -6735,15 +7236,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E103" s="2" t="n">
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
         <v>3.7921</v>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G103" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
         <is>
           <t>prj_d071db4af98d4fe1a789f8c1bb45b0e6</t>
         </is>
@@ -6770,15 +7276,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E104" s="2" t="n">
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
         <v>0.5282</v>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G104" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
         <is>
           <t>fa325ad8-92a1-460b-bebc-6e41d0744990</t>
         </is>
@@ -6805,15 +7316,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E105" s="2" t="n">
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
         <v>0.9282</v>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G105" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
         <is>
           <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
@@ -6840,15 +7356,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E106" s="2" t="n">
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
         <v>0.7305</v>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G106" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
         <is>
           <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
@@ -6875,15 +7396,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E107" s="2" t="n">
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
         <v>2.0856</v>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G107" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t>prj_4f409ce952ed458ebf2627aa06c44fad</t>
         </is>
@@ -6910,15 +7436,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E108" s="2" t="n">
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
         <v>0.758</v>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G108" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
         <is>
           <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
@@ -6945,15 +7476,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E109" s="2" t="n">
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
         <v>1.15</v>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G109" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
         <is>
           <t>prj_36eb9b5db1be4be39f04ac6563777c3c</t>
         </is>
@@ -6980,15 +7516,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E110" s="2" t="n">
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
         <v>0.096</v>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G110" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
         <is>
           <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
@@ -7015,15 +7556,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E111" s="2" t="n">
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n">
         <v>0.6592</v>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G111" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
         <is>
           <t>prj_4f409ce952ed458ebf2627aa06c44fad</t>
         </is>
@@ -7050,15 +7596,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E112" s="2" t="n">
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="n">
         <v>2.1637</v>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G112" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
         <is>
           <t>prj_1fd2a79470114b5b852f5d14a3508009</t>
         </is>
@@ -7085,15 +7636,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E113" s="2" t="n">
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n">
         <v>0.4892</v>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G113" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
         <is>
           <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
@@ -7120,15 +7676,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
         <v>2.4236</v>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G114" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
         <is>
           <t>35b02362-40b1-4e47-8bc8-2691f01f8f98</t>
         </is>
@@ -7155,15 +7716,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E115" s="2" t="n">
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n">
         <v>1.1696</v>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G115" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
         <is>
           <t>e5fccb47-d2f2-4430-97a0-88f20bb10eb7</t>
         </is>
@@ -7190,15 +7756,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
         <v>2.7512</v>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G116" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
         <is>
           <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
@@ -7225,15 +7796,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E117" s="2" t="n">
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="n">
         <v>3.6373</v>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G117" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
         <is>
           <t>prj_d071db4af98d4fe1a789f8c1bb45b0e6</t>
         </is>
@@ -7260,15 +7836,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E118" s="2" t="n">
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
         <v>3.4893</v>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G118" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
         <is>
           <t>prj_6d60ee35c5824b948b8c4dddff7c74e6</t>
         </is>
@@ -7295,15 +7876,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E119" s="2" t="n">
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n">
         <v>1.8199</v>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G119" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
         <is>
           <t>prj_51062113208340d5befa46d932c1d25e</t>
         </is>
@@ -7330,15 +7916,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E120" s="2" t="n">
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n">
         <v>1.2745</v>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G120" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
         <is>
           <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
@@ -7365,15 +7956,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E121" s="2" t="n">
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
         <v>1.7542</v>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G121" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
         <is>
           <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
@@ -7400,15 +7996,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E122" s="2" t="n">
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
         <v>0.0541</v>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G122" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
         <is>
           <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
@@ -7435,15 +8036,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E123" s="2" t="n">
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n">
         <v>0.0539</v>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G123" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
         <is>
           <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
@@ -7470,15 +8076,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E124" s="2" t="n">
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
         <v>1.3353</v>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G124" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
         <is>
           <t>prj_6d60ee35c5824b948b8c4dddff7c74e6</t>
         </is>
@@ -7505,15 +8116,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
         <v>0.0558</v>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G125" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
         <is>
           <t>prj_51062113208340d5befa46d932c1d25e</t>
         </is>
@@ -7540,15 +8156,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
         <v>0.0557</v>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G126" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
         <is>
           <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
@@ -7575,15 +8196,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
         <v>0.062</v>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G127" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
         <is>
           <t>30ca70e5-76b0-491c-bf8b-98bebafb3efd</t>
         </is>
@@ -7610,15 +8236,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E128" s="2" t="n">
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
         <v>0.0554</v>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G128" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
         <is>
           <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
@@ -7645,15 +8276,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E129" s="2" t="n">
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
         <v>0.1058</v>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G129" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
         <is>
           <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
@@ -7680,15 +8316,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E130" s="2" t="n">
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
         <v>0.5714</v>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G130" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
         <is>
           <t>prj_51062113208340d5befa46d932c1d25e</t>
         </is>
@@ -7715,15 +8356,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E131" s="2" t="n">
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n">
         <v>0.0602</v>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G131" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
         <is>
           <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
@@ -7750,15 +8396,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E132" s="2" t="n">
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
         <v>0.2581</v>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G132" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
         <is>
           <t>cea6e72d-3cf1-4e43-bfa1-3bad217a1f8f</t>
         </is>
@@ -7785,15 +8436,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E133" s="2" t="n">
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="n">
         <v>0.2173</v>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G133" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
         <is>
           <t>prj_51062113208340d5befa46d932c1d25e</t>
         </is>
@@ -7820,15 +8476,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E134" s="2" t="n">
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
         <v>0.2022</v>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G134" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
         <is>
           <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
@@ -7855,15 +8516,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E135" s="2" t="n">
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n">
         <v>0.0451</v>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G135" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
         <is>
           <t>30ca70e5-76b0-491c-bf8b-98bebafb3efd</t>
         </is>
@@ -7890,15 +8556,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E136" s="2" t="n">
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n">
         <v>0.0581</v>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G136" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
         <is>
           <t>prj_51062113208340d5befa46d932c1d25e</t>
         </is>
@@ -7925,15 +8596,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E137" s="2" t="n">
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="n">
         <v>0.065</v>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G137" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
         <is>
           <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
@@ -7960,15 +8636,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E138" s="2" t="n">
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="n">
         <v>0.1559</v>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G138" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
         <is>
           <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
@@ -7995,15 +8676,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E139" s="2" t="n">
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n">
         <v>0.0594</v>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G139" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
         <is>
           <t>prj_51062113208340d5befa46d932c1d25e</t>
         </is>
@@ -8030,15 +8716,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E140" s="2" t="n">
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n">
         <v>4.4661</v>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G140" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
         <is>
           <t>prj_b180bd849abe4731b391c1dd585be000</t>
         </is>
@@ -8065,15 +8756,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E141" s="2" t="n">
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="n">
         <v>0.5023</v>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G141" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
         <is>
           <t>prj_51062113208340d5befa46d932c1d25e</t>
         </is>
@@ -8100,15 +8796,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E142" s="2" t="n">
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n">
         <v>6.6125</v>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G142" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -8135,15 +8836,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="n">
         <v>0.1572</v>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G143" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
         <is>
           <t>cea6e72d-3cf1-4e43-bfa1-3bad217a1f8f</t>
         </is>
@@ -8170,15 +8876,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E144" s="2" t="n">
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="n">
         <v>0.4735</v>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G144" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
         <is>
           <t>prj_51062113208340d5befa46d932c1d25e</t>
         </is>
@@ -8205,15 +8916,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E145" s="2" t="n">
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="n">
         <v>0.8922</v>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G145" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
         <is>
           <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
@@ -8240,15 +8956,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E146" s="2" t="n">
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="n">
         <v>1.5767</v>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G146" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
         <is>
           <t>prj_4f409ce952ed458ebf2627aa06c44fad</t>
         </is>
@@ -8275,15 +8996,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E147" s="2" t="n">
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="n">
         <v>0.475</v>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G147" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
         <is>
           <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
@@ -8310,15 +9036,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E148" s="2" t="n">
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="n">
         <v>0.0992</v>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G148" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -8345,15 +9076,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E149" s="2" t="n">
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="n">
         <v>1.6428</v>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G149" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
         <is>
           <t>prj_b88f4c0b585642c899688ce48603ea48</t>
         </is>
@@ -8380,15 +9116,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E150" s="2" t="n">
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="n">
         <v>1.4977</v>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G150" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
         <is>
           <t>prj_07924aa5d8844a4c92ec1db23476ff4a</t>
         </is>
@@ -8415,15 +9156,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E151" s="2" t="n">
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="n">
         <v>0.8418</v>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G151" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -8450,15 +9196,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E152" s="2" t="n">
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="n">
         <v>0.0462</v>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G152" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -8485,15 +9236,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E153" s="2" t="n">
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="n">
         <v>2.207</v>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G153" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
         <is>
           <t>cea6e72d-3cf1-4e43-bfa1-3bad217a1f8f</t>
         </is>
@@ -8517,18 +9273,23 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="n">
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="n">
         <v>10.1274</v>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G154" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -8552,18 +9313,23 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="n">
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n">
         <v>1.5599</v>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G155" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
         <is>
           <t>prj_b88f4c0b585642c899688ce48603ea48</t>
         </is>
@@ -8590,15 +9356,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E156" s="2" t="n">
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="n">
         <v>0.3431</v>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G156" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
         <is>
           <t>fa55ae9f-922d-4eff-ae70-bf6acb005dbb</t>
         </is>
@@ -8625,15 +9396,20 @@
           <t>(blank)</t>
         </is>
       </c>
-      <c r="E157" s="2" t="n">
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="n">
         <v>2.0021</v>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G157" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -8657,18 +9433,23 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="n">
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="n">
         <v>7.1049</v>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G158" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
         <is>
           <t>prj_b180bd849abe4731b391c1dd585be000</t>
         </is>
@@ -8695,15 +9476,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E159" s="2" t="n">
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="n">
         <v>4.4717</v>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G159" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
         <is>
           <t>fa55ae9f-922d-4eff-ae70-bf6acb005dbb</t>
         </is>
@@ -8730,15 +9516,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E160" s="2" t="n">
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="n">
         <v>2.7574</v>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G160" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -8765,15 +9556,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E161" s="2" t="n">
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="n">
         <v>1.9321</v>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G161" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
         <is>
           <t>730ceb72-ce18-4665-aeb1-94ca18c2a89c</t>
         </is>
@@ -8797,18 +9593,23 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="n">
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="n">
         <v>7.3752</v>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G162" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
         <is>
           <t>prj_7782ae176a0f4d33bbee7296d3956151</t>
         </is>
@@ -8835,15 +9636,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E163" s="2" t="n">
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="n">
         <v>1.0198</v>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G163" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -8870,15 +9676,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E164" s="2" t="n">
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="n">
         <v>2.372</v>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G164" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
         <is>
           <t>prj_12917802ae254e84b005def4535aeaef</t>
         </is>
@@ -8905,15 +9716,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E165" s="2" t="n">
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="n">
         <v>6.7641</v>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G165" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -8940,15 +9756,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E166" s="2" t="n">
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="n">
         <v>6.177</v>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G166" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
         <is>
           <t>fa325ad8-92a1-460b-bebc-6e41d0744990</t>
         </is>
@@ -8975,15 +9796,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E167" s="2" t="n">
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="n">
         <v>0.292</v>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G167" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -9010,15 +9836,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E168" s="2" t="n">
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="n">
         <v>2.2752</v>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G168" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
         <is>
           <t>prj_b88f4c0b585642c899688ce48603ea48</t>
         </is>
@@ -9045,15 +9876,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E169" s="2" t="n">
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="n">
         <v>0.2154</v>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G169" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
         <is>
           <t>prj_12917802ae254e84b005def4535aeaef</t>
         </is>
@@ -9080,15 +9916,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E170" s="2" t="n">
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="n">
         <v>0.2258</v>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G170" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -9115,15 +9956,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E171" s="2" t="n">
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="n">
         <v>4.3872</v>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G171" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
         <is>
           <t>3296f689-9bf7-44b2-bb76-171ca01186a3</t>
         </is>
@@ -9150,15 +9996,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E172" s="2" t="n">
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="n">
         <v>0.0558</v>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G172" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
         <is>
           <t>240f17e1-96dc-45eb-86f8-9032fa60ce02</t>
         </is>
@@ -9185,15 +10036,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E173" s="2" t="n">
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="n">
         <v>1.9346</v>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G173" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
         <is>
           <t>9f23a6c7-a167-4b13-aa92-58e43f20cb1d</t>
         </is>
@@ -9220,15 +10076,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E174" s="2" t="n">
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="n">
         <v>0.0596</v>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G174" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
         <is>
           <t>prj_12917802ae254e84b005def4535aeaef</t>
         </is>
@@ -9255,15 +10116,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E175" s="2" t="n">
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="n">
         <v>0.1208</v>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G175" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
         <is>
           <t>prj_12917802ae254e84b005def4535aeaef</t>
         </is>
@@ -9287,18 +10153,23 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="n">
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="n">
         <v>0.5125999999999999</v>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G176" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -9325,15 +10196,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E177" s="2" t="n">
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="n">
         <v>3.4416</v>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G177" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -9360,15 +10236,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E178" s="2" t="n">
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="n">
         <v>0.0606</v>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G178" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
         <is>
           <t>prj_55c6fa88a091493592ad068707740160</t>
         </is>
@@ -9395,15 +10276,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E179" s="2" t="n">
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="n">
         <v>0.1792</v>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G179" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
         <is>
           <t>9f23a6c7-a167-4b13-aa92-58e43f20cb1d</t>
         </is>
@@ -9430,15 +10316,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E180" s="2" t="n">
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="n">
         <v>0.5393</v>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G180" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -9465,15 +10356,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E181" s="2" t="n">
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="n">
         <v>0.2567</v>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G181" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -9500,15 +10396,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E182" s="2" t="n">
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="n">
         <v>0.0707</v>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G182" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
         <is>
           <t>prj_d2953e5b401b46e7bbb69676b77c602a</t>
         </is>
@@ -9535,15 +10436,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E183" s="2" t="n">
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="n">
         <v>3.2164</v>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G183" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -9570,15 +10476,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E184" s="2" t="n">
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="n">
         <v>4.1514</v>
       </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G184" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
         <is>
           <t>730ceb72-ce18-4665-aeb1-94ca18c2a89c</t>
         </is>
@@ -9605,15 +10516,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E185" s="2" t="n">
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="n">
         <v>1.0377</v>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G185" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -9640,15 +10556,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E186" s="2" t="n">
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="n">
         <v>6.1404</v>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G186" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
         <is>
           <t>3296f689-9bf7-44b2-bb76-171ca01186a3</t>
         </is>
@@ -9672,18 +10593,23 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="n">
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="n">
         <v>10.6238</v>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G187" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -9710,15 +10636,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E188" s="2" t="n">
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="n">
         <v>2.3027</v>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G188" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -9745,15 +10676,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E189" s="2" t="n">
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="n">
         <v>0.2098</v>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G189" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -9780,15 +10716,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E190" s="2" t="n">
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="n">
         <v>0.3478</v>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G190" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
         <is>
           <t>prj_36eb9b5db1be4be39f04ac6563777c3c</t>
         </is>
@@ -9815,15 +10756,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E191" s="2" t="n">
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="n">
         <v>3.3181</v>
       </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G191" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
         <is>
           <t>prj_b88f4c0b585642c899688ce48603ea48</t>
         </is>
@@ -9850,15 +10796,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E192" s="2" t="n">
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="n">
         <v>0.0498</v>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G192" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
         <is>
           <t>prj_36eb9b5db1be4be39f04ac6563777c3c</t>
         </is>
@@ -9885,15 +10836,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E193" s="2" t="n">
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="n">
         <v>0.8645</v>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G193" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
         <is>
           <t>prj_d320c0b34bd54ff0b5cf05e31219765c</t>
         </is>
@@ -9920,15 +10876,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E194" s="2" t="n">
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="n">
         <v>0.3165</v>
       </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G194" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -9955,15 +10916,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E195" s="2" t="n">
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="n">
         <v>1.0607</v>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G195" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -9990,15 +10956,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E196" s="2" t="n">
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="n">
         <v>3.9399</v>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G196" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
         <is>
           <t>3296f689-9bf7-44b2-bb76-171ca01186a3</t>
         </is>
@@ -10025,15 +10996,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E197" s="2" t="n">
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="n">
         <v>1.5485</v>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G197" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
         <is>
           <t>prj_b88f4c0b585642c899688ce48603ea48</t>
         </is>
@@ -10060,15 +11036,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E198" s="2" t="n">
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="n">
         <v>0.2055</v>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G198" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -10095,15 +11076,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E199" s="2" t="n">
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="n">
         <v>5.9128</v>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G199" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
         <is>
           <t>9f23a6c7-a167-4b13-aa92-58e43f20cb1d</t>
         </is>
@@ -10130,15 +11116,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E200" s="2" t="n">
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="n">
         <v>4.1502</v>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G200" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
         <is>
           <t>3296f689-9bf7-44b2-bb76-171ca01186a3</t>
         </is>
@@ -10165,15 +11156,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E201" s="2" t="n">
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="n">
         <v>0.0776</v>
       </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G201" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
         <is>
           <t>9f23a6c7-a167-4b13-aa92-58e43f20cb1d</t>
         </is>
@@ -10200,15 +11196,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E202" s="2" t="n">
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="n">
         <v>1.0862</v>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G202" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -10235,15 +11236,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E203" s="2" t="n">
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="n">
         <v>2.9018</v>
       </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G203" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -10270,15 +11276,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E204" s="2" t="n">
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="n">
         <v>0.2482</v>
       </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G204" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -10305,15 +11316,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E205" s="2" t="n">
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="n">
         <v>1.7973</v>
       </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G205" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -10340,15 +11356,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E206" s="2" t="n">
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="n">
         <v>1.2916</v>
       </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G206" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -10375,15 +11396,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E207" s="2" t="n">
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="n">
         <v>0.6578000000000001</v>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G207" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
         <is>
           <t>prj_51062113208340d5befa46d932c1d25e</t>
         </is>
@@ -10410,15 +11436,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E208" s="2" t="n">
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="n">
         <v>0.3591</v>
       </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G208" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
         <is>
           <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
@@ -10445,15 +11476,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E209" s="2" t="n">
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="n">
         <v>0.0385</v>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G209" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
         <is>
           <t>c1e560cb-557a-4a72-abad-e5b7476b8810</t>
         </is>
@@ -10480,15 +11516,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E210" s="2" t="n">
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="n">
         <v>0.07439999999999999</v>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G210" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
         <is>
           <t>prj_51062113208340d5befa46d932c1d25e</t>
         </is>
@@ -10515,15 +11556,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E211" s="2" t="n">
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="n">
         <v>1.7594</v>
       </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G211" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
         <is>
           <t>52346906-65af-4401-87d9-210a31892a01</t>
         </is>
@@ -10550,15 +11596,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E212" s="2" t="n">
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="n">
         <v>0.4365</v>
       </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G212" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
         <is>
           <t>52346906-65af-4401-87d9-210a31892a01</t>
         </is>
@@ -10585,15 +11636,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E213" s="2" t="n">
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="n">
         <v>0.148</v>
       </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G213" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
         <is>
           <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
         </is>
@@ -10620,15 +11676,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E214" s="2" t="n">
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="n">
         <v>1.1246</v>
       </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G214" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
         <is>
           <t>fe8b9d27-9f88-4952-bdab-74f6301cb298</t>
         </is>
@@ -10655,15 +11716,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E215" s="2" t="n">
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="n">
         <v>9.023899999999999</v>
       </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G215" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
         <is>
           <t>prj_b180bd849abe4731b391c1dd585be000</t>
         </is>
@@ -10690,15 +11756,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E216" s="2" t="n">
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="n">
         <v>25.9825</v>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G216" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -10725,15 +11796,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E217" s="2" t="n">
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="n">
         <v>1.7379</v>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G217" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
         <is>
           <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
         </is>
@@ -10760,15 +11836,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E218" s="2" t="n">
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="n">
         <v>0.2638</v>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G218" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -10795,15 +11876,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E219" s="2" t="n">
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="n">
         <v>0.2711</v>
       </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G219" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -10827,18 +11913,23 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>(blank)</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="n">
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="n">
         <v>1.3651</v>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G220" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
         <is>
           <t>b02be0c1-41f9-4b64-bd16-92af548b6460</t>
         </is>
@@ -10865,15 +11956,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E221" s="2" t="n">
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="n">
         <v>0.3334</v>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G221" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
         <is>
           <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
         </is>
@@ -10900,15 +11996,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E222" s="2" t="n">
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="n">
         <v>3.0136</v>
       </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G222" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -10935,15 +12036,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E223" s="2" t="n">
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="n">
         <v>0.1088</v>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G223" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
         <is>
           <t>63389cd5-92cf-45f5-b3eb-325d934e47bb</t>
         </is>
@@ -10970,15 +12076,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E224" s="2" t="n">
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="n">
         <v>1.3795</v>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G224" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
         <is>
           <t>b02be0c1-41f9-4b64-bd16-92af548b6460</t>
         </is>
@@ -11005,15 +12116,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E225" s="2" t="n">
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="n">
         <v>0.4905</v>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G225" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
         <is>
           <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
         </is>
@@ -11040,15 +12156,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E226" s="2" t="n">
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="n">
         <v>0.9993</v>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G226" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -11075,15 +12196,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E227" s="2" t="n">
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="n">
         <v>3.4427</v>
       </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G227" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -11110,15 +12236,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E228" s="2" t="n">
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="n">
         <v>3.3617</v>
       </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G228" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -11145,15 +12276,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E229" s="2" t="n">
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="n">
         <v>2.2429</v>
       </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G229" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
         <is>
           <t>prj_4f409ce952ed458ebf2627aa06c44fad</t>
         </is>
@@ -11180,15 +12316,20 @@
           <t>claude-sonnet-4-6</t>
         </is>
       </c>
-      <c r="E230" s="2" t="n">
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="n">
         <v>6.1008</v>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G230" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
         <is>
           <t>prj_b180bd849abe4731b391c1dd585be000</t>
         </is>
@@ -11215,15 +12356,20 @@
           <t>claude-opus-4-6</t>
         </is>
       </c>
-      <c r="E231" s="2" t="n">
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="n">
         <v>6.7566</v>
       </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="G231" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
         <is>
           <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
         </is>
@@ -11296,7 +12442,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(blank), claude-opus-4-6</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
     </row>
@@ -11319,7 +12465,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(blank), claude-sonnet-4-6</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -11388,7 +12534,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(blank), claude-sonnet-4-6</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -11411,7 +12557,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(blank), claude-opus-4-6, claude-sonnet-4-6</t>
+          <t>claude-opus-4-6, claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -11595,7 +12741,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -11986,7 +13132,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(blank), claude-sonnet-4-6</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -12649,16 +13795,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>198.17</v>
+        <v>219.17</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.1522</v>
+        <v>1.2313</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>9.02</v>
@@ -12671,16 +13817,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>102.73</v>
+        <v>123.99</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.7033</v>
+        <v>3.0242</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>25.98</v>
@@ -12693,19 +13839,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46.61</v>
+        <v>4.34</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.2369</v>
+        <v>2.1694</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>10.62</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="5">

--- a/reports/hackathon-2026-07-26/hackathon_cost_breakdown.xlsx
+++ b/reports/hackathon-2026-07-26/hackathon_cost_breakdown.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>95.20999999999999</v>
+        <v>157.85</v>
       </c>
       <c r="G2" t="n">
-        <v>27.1</v>
+        <v>30</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -532,27 +532,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>toledosean@gmail.com</t>
+          <t>stevenyang.dev@gmail.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sean T</t>
+          <t>syang0624</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>toledosean@gmail.com</t>
+          <t>stevenyang.dev@gmail.com</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>29.69</v>
+        <v>72.45</v>
       </c>
       <c r="G3" t="n">
-        <v>8.4</v>
+        <v>13.8</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -575,13 +575,13 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>26.7</v>
+        <v>35.19</v>
       </c>
       <c r="G4" t="n">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -598,34 +598,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>stevenyang.dev@gmail.com</t>
+          <t>toledosean@gmail.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>syang0624</t>
+          <t>Sean T</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>stevenyang.dev@gmail.com</t>
+          <t>toledosean@gmail.com</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>18.62</v>
+        <v>29.69</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6, claude-opus-4-6</t>
+          <t>claude-opus-4-6, (blank), claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         <v>15.21</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -692,7 +692,7 @@
         <v>14.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -709,34 +709,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sahasrakokkula77@gmail.com</t>
+          <t>kshitijatus@gmail.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>K-SAHASRA</t>
+          <t>Kshitij</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sahasrakokkula77@gmail.com</t>
+          <t>kshitijatus@gmail.com</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>12.17</v>
+        <v>13.98</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
     </row>
@@ -746,27 +746,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>philipnisevich@gmail.com</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Philip Nisevich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>philipnisevich@gmail.com</t>
-        </is>
-      </c>
+          <t>anon:2680c3ce</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>11.76</v>
+        <v>12.83</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -783,27 +775,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>enochfyw@gmail.com</t>
+          <t>sahasrakokkula77@gmail.com</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>eyfung</t>
+          <t>K-SAHASRA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>enochfyw@gmail.com</t>
+          <t>sahasrakokkula77@gmail.com</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>10.53</v>
+        <v>12.17</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -820,27 +812,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kakanisnehil@gmail.com</t>
+          <t>philipnisevich@gmail.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>snek152</t>
+          <t>Philip Nisevich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>kakanisnehil@gmail.com</t>
+          <t>philipnisevich@gmail.com</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>8.279999999999999</v>
+        <v>11.76</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -857,27 +849,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>noriaki@uni.minerva.edu</t>
+          <t>umangshankar10@gmail.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Noriaki Kishida</t>
+          <t>Umang3211</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>noriaki@uni.minerva.edu</t>
+          <t>umangshankar10@gmail.com</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8.1</v>
+        <v>10.54</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -894,34 +886,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>owin@owinrojas.com</t>
+          <t>enochfyw@gmail.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Owin Rojas</t>
+          <t>eyfung</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>owin@owinrojas.com</t>
+          <t>enochfyw@gmail.com</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>7.58</v>
+        <v>10.53</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>claude-opus-4-6, claude-sonnet-4-6</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -931,27 +923,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>umangshankar10@gmail.com</t>
+          <t>kakanisnehil@gmail.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Umang3211</t>
+          <t>snek152</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>umangshankar10@gmail.com</t>
+          <t>kakanisnehil@gmail.com</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>2</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>7.43</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -968,27 +960,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>stepodkelly@gmail.com</t>
+          <t>noriaki@uni.minerva.edu</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stephen Kelly</t>
+          <t>Noriaki Kishida</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>stepodkelly@gmail.com</t>
+          <t>noriaki@uni.minerva.edu</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>7.38</v>
+        <v>8.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1005,27 +997,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>amyhsieh3730@gmail.com</t>
+          <t>benjinisevich2@gmail.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>amyxhsieh</t>
+          <t>benji nisevich2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>amyhsieh3730@gmail.com</t>
+          <t>benjinisevich2@gmail.com</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>7</v>
+        <v>7.89</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1042,34 +1034,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nagatarunmoturi@gmail.com</t>
+          <t>owin@owinrojas.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tarun Moturi</t>
+          <t>Owin Rojas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>nagatarunmoturi@gmail.com</t>
+          <t>owin@owinrojas.com</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>6.7</v>
+        <v>7.58</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>claude-opus-4-6, claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -1079,27 +1071,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>clai74@mail.ccsf.edu</t>
+          <t>stepodkelly@gmail.com</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chineseman Lai</t>
+          <t>Stephen Kelly</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>clai74@mail.ccsf.edu</t>
+          <t>stepodkelly@gmail.com</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6.08</v>
+        <v>7.38</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1116,27 +1108,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>benjinisevich2@gmail.com</t>
+          <t>amyhsieh3730@gmail.com</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>benji nisevich2</t>
+          <t>amyxhsieh</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>benjinisevich2@gmail.com</t>
+          <t>amyhsieh3730@gmail.com</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>5.23</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1153,19 +1145,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>anon:2680c3ce</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>nagatarunmoturi@gmail.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tarun Moturi</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>nagatarunmoturi@gmail.com</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4.96</v>
+        <v>6.7</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1182,27 +1182,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mborgiottitulane@gmail.com</t>
+          <t>clai74@mail.ccsf.edu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Max Borgiotti</t>
+          <t>Chineseman Lai</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>mborgiottitulane@gmail.com</t>
+          <t>clai74@mail.ccsf.edu</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>2</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>4.81</v>
+        <v>6.08</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1219,23 +1219,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rosekr1</t>
+          <t>mborgiottitulane@gmail.com</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rosekr1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Max Borgiotti</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>mborgiottitulane@gmail.com</t>
+        </is>
+      </c>
       <c r="E22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4.49</v>
+        <v>4.81</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1252,27 +1256,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>kewinszlezingier@gmail.com</t>
+          <t>Rosekr1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kewin Szlezingier</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>kewinszlezingier@gmail.com</t>
-        </is>
-      </c>
+          <t>Rosekr1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>4.23</v>
+        <v>4.49</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1289,27 +1289,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>misha@mypipdev.com</t>
+          <t>kewinszlezingier@gmail.com</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Misha Stastna</t>
+          <t>Kewin Szlezingier</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>misha@mypipdev.com</t>
+          <t>kewinszlezingier@gmail.com</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="G24" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1326,27 +1326,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>amberkaurtoor@gmail.com</t>
+          <t>misha@mypipdev.com</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Amber Toor</t>
+          <t>Misha Stastna</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>amberkaurtoor@gmail.com</t>
+          <t>misha@mypipdev.com</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1363,34 +1363,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>schan119@calpoly.edu</t>
+          <t>phongct1105@gmail.com</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>samsonchang2028</t>
+          <t>PhongCT1105</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>schan119@calpoly.edu</t>
+          <t>phongct1105@gmail.com</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>4.04</v>
+        <v>4.12</v>
       </c>
       <c r="G26" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>claude-sonnet-4-6, (blank)</t>
         </is>
       </c>
     </row>
@@ -1400,27 +1400,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yujiwork@outlook.com</t>
+          <t>amberkaurtoor@gmail.com</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>yojijoestar</t>
+          <t>Amber Toor</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>yujiwork@outlook.com</t>
+          <t>amberkaurtoor@gmail.com</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="G27" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1437,34 +1437,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sohamjani8@gmail.com</t>
+          <t>schan119@calpoly.edu</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sohamtjani</t>
+          <t>samsonchang2028</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>sohamjani8@gmail.com</t>
+          <t>schan119@calpoly.edu</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>2</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>3.18</v>
+        <v>4.04</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>gpt-5.4</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -1474,24 +1474,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ryanxu240@gmail.com</t>
+          <t>yujiwork@outlook.com</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>rxu240</t>
+          <t>yojijoestar</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ryanxu240@gmail.com</t>
+          <t>yujiwork@outlook.com</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>0.8</v>
@@ -1511,34 +1511,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>142857tom@gmail.com</t>
+          <t>sohamjani8@gmail.com</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Shockwave Thomas</t>
+          <t>sohamtjani</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>142857tom@gmail.com</t>
+          <t>sohamjani8@gmail.com</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>2.62</v>
+        <v>3.18</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
@@ -1548,34 +1548,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>manidweepsharma1801@gmail.com</t>
+          <t>rishabh.rb@icloud.com</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>manidweep sharma</t>
+          <t>rishabhcli</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>manidweepsharma1801@gmail.com</t>
+          <t>rishabh.rb@icloud.com</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>2.41</v>
+        <v>3.12</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6, gpt-5.2</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -1585,34 +1585,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wanzelin007@gmail.com</t>
+          <t>atharavhedage@gmail.com</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Zelin Wan</t>
+          <t>Atharav Hedage</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>wanzelin007@gmail.com</t>
+          <t>atharavhedage@gmail.com</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -1622,24 +1622,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>rishabh.rb@icloud.com</t>
+          <t>Matthew.you.2520@gmail.com</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rishabhcli</t>
+          <t>NonOxC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>rishabh.rb@icloud.com</t>
+          <t>Matthew.you.2520@gmail.com</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="G33" t="n">
         <v>0.6</v>
@@ -1659,34 +1659,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>kshitijatus@gmail.com</t>
+          <t>ryanxu240@gmail.com</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kshitij</t>
+          <t>rxu240</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>kshitijatus@gmail.com</t>
+          <t>ryanxu240@gmail.com</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1.12</v>
+        <v>2.74</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -1696,27 +1696,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>tiwari.aadi123@gmail.com</t>
+          <t>142857tom@gmail.com</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Aadi Tiwari</t>
+          <t>Shockwave Thomas</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiwari.aadi123@gmail.com</t>
+          <t>142857tom@gmail.com</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.86</v>
+        <v>2.62</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1733,34 +1733,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>likhith11ramesh@gmail.com</t>
+          <t>arshmeetsodhi@gmail.com</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Likhith Ramesha</t>
+          <t>Arshmeet Sodhi</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>likhith11ramesh@gmail.com</t>
+          <t>arshmeetsodhi@gmail.com</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.68</v>
+        <v>2.47</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>gpt-5.2, claude-opus-4-5-20251101</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -1770,34 +1770,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ryanandnoahlee@gmail.com</t>
+          <t>manidweepsharma1801@gmail.com</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>comp-Ryan</t>
+          <t>manidweep sharma</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ryanandnoahlee@gmail.com</t>
+          <t>manidweepsharma1801@gmail.com</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.24</v>
+        <v>2.41</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>claude-sonnet-4-6, gpt-5.2</t>
         </is>
       </c>
     </row>
@@ -1807,34 +1807,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>sahilnale@icloud.com</t>
+          <t>wanzelin007@gmail.com</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sahilnale</t>
+          <t>Zelin Wan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>sahilnale@icloud.com</t>
+          <t>wanzelin007@gmail.com</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.18</v>
+        <v>2.34</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>(blank)</t>
         </is>
       </c>
     </row>
@@ -1844,27 +1844,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>cajuliawan@gmail.com</t>
+          <t>neil_shah@my.cuesta.edu</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Julia Wan</t>
+          <t>Neil Shah</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>cajuliawan@gmail.com</t>
+          <t>neil_shah@my.cuesta.edu</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.13</v>
+        <v>2.32</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1881,34 +1881,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>aneeshpradhan@acm.org</t>
+          <t>praniil.nagaraj@gmail.com</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>aneesh-pradhan</t>
+          <t>Praniil Nagaraj</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>aneeshpradhan@acm.org</t>
+          <t>praniil.nagaraj@gmail.com</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.12</v>
+        <v>1.67</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
     </row>
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>harshjannawar14@gmail.com</t>
+          <t>fkw155@mun.ca</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>harsh jannawar</t>
+          <t>frankie-eight-days</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>harshjannawar14@gmail.com</t>
+          <t>fkw155@mun.ca</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.11</v>
+        <v>1.32</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1955,34 +1955,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>chengreric@gmail.com</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>陈冠荣</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>chengreric@gmail.com</t>
-        </is>
-      </c>
+          <t>anon:23f87ab2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.11</v>
+        <v>1.28</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>(blank)</t>
         </is>
       </c>
     </row>
@@ -1992,27 +1984,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>samrocksnature@gmail.com</t>
+          <t>sahilnale@icloud.com</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>samrocksnature</t>
+          <t>sahilnale</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>samrocksnature@gmail.com</t>
+          <t>sahilnale@icloud.com</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.06</v>
+        <v>1.11</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2029,27 +2021,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>lee.anastasia.y@gmail.com</t>
+          <t>aakashryback@gmail.com</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>alee51</t>
+          <t>vidiyala99</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>lee.anastasia.y@gmail.com</t>
+          <t>aakashryback@gmail.com</t>
         </is>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.04</v>
+        <v>1.01</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2066,32 +2058,513 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>mp@gmail.com</t>
+          <t>tiwari.aadi123@gmail.com</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mp@gmail.com</t>
+          <t>Aadi Tiwari</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>mp@gmail.com</t>
+          <t>tiwari.aadi123@gmail.com</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.03</v>
+        <v>0.86</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>walterchen.ca@gmail.com</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Walter Chen</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>walterchen.ca@gmail.com</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>likhith11ramesh@gmail.com</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Likhith Ramesha</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>likhith11ramesh@gmail.com</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>gpt-5.2, claude-opus-4-5-20251101</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>samrocksnature@gmail.com</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>samrocksnature</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>samrocksnature@gmail.com</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ryanandnoahlee@gmail.com</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>comp-Ryan</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Ryanandnoahlee@gmail.com</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>cajuliawan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Julia Wan</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>cajuliawan@gmail.com</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>aneeshpradhan@acm.org</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>aneesh-pradhan</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>aneeshpradhan@acm.org</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>harshjannawar14@gmail.com</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>harsh jannawar</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>harshjannawar14@gmail.com</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>chengreric@gmail.com</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>陈冠荣</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>chengreric@gmail.com</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>jczhang223@gmail.com</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Jaden Zhang</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>jczhang223@gmail.com</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>visheshv05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Vishesh Verma</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>visheshv05@gmail.com</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>lee.anastasia.y@gmail.com</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>alee51</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>lee.anastasia.y@gmail.com</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>mp@gmail.com</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>mp@gmail.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>mp@gmail.com</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ayaan.chawla@gmail.com</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ayaan C</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ayaan.chawla@gmail.com</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
         <is>
           <t>claude-sonnet-4-6</t>
         </is>
@@ -2108,7 +2581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2176,16 +2649,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>95.20999999999999</v>
+        <v>157.85</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>8.9</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>86.31</v>
+        <v>148.95</v>
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -2195,23 +2668,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>toledosean@gmail.com</t>
+          <t>stevenyang.dev@gmail.com</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>29.69</v>
+        <v>72.45</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.01</v>
+        <v>14.47</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>26.67</v>
+        <v>37.97</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>20.01</v>
       </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
@@ -2224,13 +2697,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>26.7</v>
+        <v>35.19</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>26.7</v>
+        <v>35.19</v>
       </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
@@ -2241,22 +2714,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>stevenyang.dev@gmail.com</t>
+          <t>toledosean@gmail.com</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>18.62</v>
+        <v>29.69</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>14.47</v>
+        <v>1.01</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>26.67</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
@@ -2308,19 +2783,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sahasrakokkula77@gmail.com</t>
+          <t>kshitijatus@gmail.com</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="E8" s="2" t="n"/>
+        <v>13.98</v>
+      </c>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>13.98</v>
+      </c>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
@@ -2329,17 +2804,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>philipnisevich@gmail.com</t>
+          <t>anon:2680c3ce</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>11.76</v>
+        <v>12.83</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11.76</v>
+        <v>12.83</v>
       </c>
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
@@ -2350,17 +2825,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>enochfyw@gmail.com</t>
+          <t>sahasrakokkula77@gmail.com</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>10.53</v>
+        <v>12.17</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10.53</v>
+        <v>12.17</v>
       </c>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
@@ -2371,17 +2846,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kakanisnehil@gmail.com</t>
+          <t>philipnisevich@gmail.com</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>8.279999999999999</v>
+        <v>11.76</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8.279999999999999</v>
+        <v>11.76</v>
       </c>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
@@ -2392,17 +2867,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>noriaki@uni.minerva.edu</t>
+          <t>umangshankar10@gmail.com</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>8.1</v>
+        <v>10.54</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8.1</v>
+        <v>10.54</v>
       </c>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
@@ -2413,21 +2888,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>owin@owinrojas.com</t>
+          <t>enochfyw@gmail.com</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7.58</v>
+        <v>10.53</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>4.09</v>
-      </c>
+        <v>10.53</v>
+      </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
@@ -2436,17 +2909,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>umangshankar10@gmail.com</t>
+          <t>kakanisnehil@gmail.com</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7.43</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7.43</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
@@ -2457,17 +2930,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>stepodkelly@gmail.com</t>
+          <t>noriaki@uni.minerva.edu</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7.38</v>
+        <v>8.1</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7.38</v>
+        <v>8.1</v>
       </c>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
@@ -2478,17 +2951,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>amyhsieh3730@gmail.com</t>
+          <t>benjinisevich2@gmail.com</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>7</v>
+        <v>7.89</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7</v>
+        <v>7.89</v>
       </c>
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
@@ -2499,19 +2972,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nagatarunmoturi@gmail.com</t>
+          <t>owin@owinrojas.com</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6.7</v>
+        <v>7.58</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E17" s="2" t="n"/>
+        <v>3.49</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>4.09</v>
+      </c>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
@@ -2520,17 +2995,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>clai74@mail.ccsf.edu</t>
+          <t>stepodkelly@gmail.com</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6.08</v>
+        <v>7.38</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6.08</v>
+        <v>7.38</v>
       </c>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
@@ -2541,17 +3016,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>benjinisevich2@gmail.com</t>
+          <t>amyhsieh3730@gmail.com</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>5.23</v>
+        <v>7</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>5.23</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
@@ -2562,17 +3037,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>anon:2680c3ce</t>
+          <t>nagatarunmoturi@gmail.com</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4.96</v>
+        <v>6.7</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4.96</v>
+        <v>6.7</v>
       </c>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
@@ -2583,17 +3058,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mborgiottitulane@gmail.com</t>
+          <t>clai74@mail.ccsf.edu</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>4.81</v>
+        <v>6.08</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4.81</v>
+        <v>6.08</v>
       </c>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
@@ -2604,17 +3079,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rosekr1</t>
+          <t>mborgiottitulane@gmail.com</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>4.49</v>
+        <v>4.81</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4.49</v>
+        <v>4.81</v>
       </c>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
@@ -2625,17 +3100,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kewinszlezingier@gmail.com</t>
+          <t>Rosekr1</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>4.23</v>
+        <v>4.49</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4.23</v>
+        <v>4.49</v>
       </c>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
@@ -2646,17 +3121,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>misha@mypipdev.com</t>
+          <t>kewinszlezingier@gmail.com</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
@@ -2667,17 +3142,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>amberkaurtoor@gmail.com</t>
+          <t>misha@mypipdev.com</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
@@ -2688,20 +3163,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>schan119@calpoly.edu</t>
+          <t>phongct1105@gmail.com</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>4.04</v>
+        <v>4.12</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4.04</v>
+        <v>2.36</v>
       </c>
       <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
+      <c r="F26" s="2" t="n">
+        <v>1.76</v>
+      </c>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
@@ -2709,17 +3186,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yujiwork@outlook.com</t>
+          <t>amberkaurtoor@gmail.com</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
@@ -2730,38 +3207,38 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sohamjani8@gmail.com</t>
+          <t>schan119@calpoly.edu</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+        <v>4.04</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>4.04</v>
+      </c>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n">
-        <v>3.18</v>
-      </c>
+      <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ryanxu240@gmail.com</t>
+          <t>yujiwork@outlook.com</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
@@ -2772,64 +3249,62 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>142857tom@gmail.com</t>
+          <t>sohamjani8@gmail.com</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>2.62</v>
-      </c>
+        <v>3.18</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
+      <c r="G30" s="2" t="n">
+        <v>3.18</v>
+      </c>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>manidweepsharma1801@gmail.com</t>
+          <t>rishabh.rb@icloud.com</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2.41</v>
+        <v>3.12</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2.02</v>
+        <v>3.12</v>
       </c>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n">
-        <v>0.39</v>
-      </c>
+      <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>wanzelin007@gmail.com</t>
+          <t>atharavhedage@gmail.com</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+        <v>3.05</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>3.05</v>
+      </c>
       <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n">
-        <v>2.34</v>
-      </c>
+      <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
@@ -2837,17 +3312,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>rishabh.rb@icloud.com</t>
+          <t>Matthew.you.2520@gmail.com</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
@@ -2858,19 +3333,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kshitijatus@gmail.com</t>
+          <t>ryanxu240@gmail.com</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n">
-        <v>1.12</v>
-      </c>
+        <v>2.74</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
@@ -2879,17 +3354,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tiwari.aadi123@gmail.com</t>
+          <t>142857tom@gmail.com</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.86</v>
+        <v>2.62</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.86</v>
+        <v>2.62</v>
       </c>
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
@@ -2900,64 +3375,64 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>likhith11ramesh@gmail.com</t>
+          <t>arshmeetsodhi@gmail.com</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+        <v>2.47</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>2.47</v>
+      </c>
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ryanandnoahlee@gmail.com</t>
+          <t>manidweepsharma1801@gmail.com</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.24</v>
+        <v>2.41</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.24</v>
+        <v>2.02</v>
       </c>
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="H37" s="2" t="n">
+        <v>0.39</v>
+      </c>
       <c r="I37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sahilnale@icloud.com</t>
+          <t>wanzelin007@gmail.com</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>0.18</v>
-      </c>
+        <v>2.34</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
+      <c r="F38" s="2" t="n">
+        <v>2.34</v>
+      </c>
       <c r="G38" s="2" t="n"/>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
@@ -2965,17 +3440,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cajuliawan@gmail.com</t>
+          <t>neil_shah@my.cuesta.edu</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>0.13</v>
+        <v>2.32</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.13</v>
+        <v>2.32</v>
       </c>
       <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="n"/>
@@ -2986,19 +3461,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>aneeshpradhan@acm.org</t>
+          <t>praniil.nagaraj@gmail.com</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E40" s="2" t="n"/>
+        <v>1.67</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n">
+        <v>1.67</v>
+      </c>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
@@ -3007,17 +3482,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>harshjannawar14@gmail.com</t>
+          <t>fkw155@mun.ca</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.11</v>
+        <v>1.32</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.11</v>
+        <v>1.32</v>
       </c>
       <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
@@ -3028,20 +3503,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>chengreric@gmail.com</t>
+          <t>anon:23f87ab2</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>0.11</v>
-      </c>
+        <v>1.28</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
+      <c r="F42" s="2" t="n">
+        <v>1.28</v>
+      </c>
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
@@ -3049,17 +3524,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>samrocksnature@gmail.com</t>
+          <t>sahilnale@icloud.com</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>0.06</v>
+        <v>1.11</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.06</v>
+        <v>1.11</v>
       </c>
       <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
@@ -3070,17 +3545,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>lee.anastasia.y@gmail.com</t>
+          <t>aakashryback@gmail.com</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0.04</v>
+        <v>1.01</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.04</v>
+        <v>1.01</v>
       </c>
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
@@ -3091,23 +3566,298 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>mp@gmail.com</t>
+          <t>tiwari.aadi123@gmail.com</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.03</v>
+        <v>0.86</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.03</v>
+        <v>0.86</v>
       </c>
       <c r="E45" s="2" t="n"/>
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>walterchen.ca@gmail.com</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>likhith11ramesh@gmail.com</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>samrocksnature@gmail.com</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Ryanandnoahlee@gmail.com</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cajuliawan@gmail.com</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>aneeshpradhan@acm.org</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>harshjannawar14@gmail.com</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>chengreric@gmail.com</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>jczhang223@gmail.com</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>visheshv05@gmail.com</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>lee.anastasia.y@gmail.com</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>mp@gmail.com</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ayaan.chawla@gmail.com</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3120,7 +3870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H231"/>
+  <dimension ref="A1:H302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -12375,6 +13125,2846 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:34</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:04</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>4.1383</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:37</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:07</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>jczhang223@gmail.com</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="n">
+        <v>0.0844</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>6ea9e44e-bc7f-465b-94a6-5044f8507a6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:38</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:08</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>4.2143</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:41</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:11</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>anon:2680c3ce</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="n">
+        <v>4.9887</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>prj_36eb9b5db1be4be39f04ac6563777c3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:42</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:12</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="n">
+        <v>0.8802</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:45</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:15</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>kshitijatus@gmail.com</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>0.8258</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>fe8b9d27-9f88-4952-bdab-74f6301cb298</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:48</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:18</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>fkw155@mun.ca</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>1.3164</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>dccc4223-c2a9-4dea-8f36-9499b046eef6</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:52</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:22</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="n">
+        <v>2.5562</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>6493a4ed-eb46-4283-9b74-c40698d83caa</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:53</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:23</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="n">
+        <v>8.4704</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:54</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:24</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>kshitijatus@gmail.com</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>1.3809</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>fe8b9d27-9f88-4952-bdab-74f6301cb298</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:54</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:24</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="n">
+        <v>0.4947</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>6493a4ed-eb46-4283-9b74-c40698d83caa</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:54</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:24</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Rafael Lopez</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="n">
+        <v>8.3207</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>prj_b180bd849abe4731b391c1dd585be000</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:56</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:26</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>sahilnale@icloud.com</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>0.9298</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>prj_e0a8e92dbfa14efebfe76d073967ae58</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:56</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:26</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>arshmeetsodhi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>8c32b563-ccaa-4bb0-8ffa-b135bbf688d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:57</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:27</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>anon:2680c3ce</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>0.5465</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>prj_c650bb9fe85c46129b6250e1e9103c2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:58</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:28</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Rafael Lopez</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>prj_b180bd849abe4731b391c1dd585be000</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:00</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:30</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>anon:2680c3ce</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>prj_c650bb9fe85c46129b6250e1e9103c2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:01</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:31</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>anon:2680c3ce</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>0.1189</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>prj_c650bb9fe85c46129b6250e1e9103c2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:02</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:32</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>kshitijatus@gmail.com</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>fe8b9d27-9f88-4952-bdab-74f6301cb298</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:03</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:33</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>arshmeetsodhi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="n">
+        <v>0.6503</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>8c32b563-ccaa-4bb0-8ffa-b135bbf688d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:04</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:34</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>10.6719</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:05</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:35</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>samrocksnature@gmail.com</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>f84bedd1-4803-4190-b89c-c72f7deffdfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:09</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:39</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>stevenyang.dev@gmail.com</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="n">
+        <v>19.9718</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>3296f689-9bf7-44b2-bb76-171ca01186a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:10</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:40</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>kshitijatus@gmail.com</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="n">
+        <v>2.0081</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>fe8b9d27-9f88-4952-bdab-74f6301cb298</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:12</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:42</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>arshmeetsodhi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>1.1868</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>8c32b563-ccaa-4bb0-8ffa-b135bbf688d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:12</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:42</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="n">
+        <v>0.9199000000000001</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:15</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:45</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:19</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:49</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>kshitijatus@gmail.com</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>2.0928</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>fe8b9d27-9f88-4952-bdab-74f6301cb298</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:20</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:50</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>10.0785</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:26</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:56</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>kshitijatus@gmail.com</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>2.2944</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>fe8b9d27-9f88-4952-bdab-74f6301cb298</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:28</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:58</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>3.9429</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:29</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-07-27 06:59</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>0.4951</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:30</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="n">
+        <v>0.8955</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>8537287b-c8a9-4cbc-bb5f-3d17146dd750</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:32</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:02</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>8537287b-c8a9-4cbc-bb5f-3d17146dd750</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:33</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:03</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>kshitijatus@gmail.com</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>1.6952</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>fe8b9d27-9f88-4952-bdab-74f6301cb298</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:34</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:04</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>6.1144</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:35</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:05</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>recovered</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>8537287b-c8a9-4cbc-bb5f-3d17146dd750</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:37</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:07</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="n">
+        <v>0.4704</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:39</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:09</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:43</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:13</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>visheshv05@gmail.com</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>47d22643-2cf7-4828-88f5-be4eb756755f</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:43</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:13</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>stevenyang.dev@gmail.com</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="n">
+        <v>20.0071</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>3296f689-9bf7-44b2-bb76-171ca01186a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:43</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:13</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>anon:23f87ab2</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="n">
+        <v>1.2764</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>8a3b0c74-939b-41ee-bd4b-7ed78557ab9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:44</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:14</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="n">
+        <v>9.6143</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:45</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:15</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="n">
+        <v>0.1472</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:47</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:17</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="n">
+        <v>1.7563</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>8537287b-c8a9-4cbc-bb5f-3d17146dd750</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:47</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:17</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="n">
+        <v>1.7706</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:50</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:20</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="n">
+        <v>1.4446</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:51</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:21</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="n">
+        <v>0.2283</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>8537287b-c8a9-4cbc-bb5f-3d17146dd750</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:53</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:23</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>rishabh.rb@icloud.com</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="n">
+        <v>0.6304999999999999</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>52346906-65af-4401-87d9-210a31892a01</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:54</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:24</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:55</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:25</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:55</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:25</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>rishabh.rb@icloud.com</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>52346906-65af-4401-87d9-210a31892a01</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:56</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:26</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:04</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:34</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>praniil.nagaraj@gmail.com</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="n">
+        <v>1.6746</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>d0698e37-e8f0-4255-83a3-02c9c3538473</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:05</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:35</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>anon:2680c3ce</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>1.8325</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>prj_7f47a9f20bd94002b1f0e429add9e952</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:06</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:36</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="n">
+        <v>0.6052999999999999</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>8537287b-c8a9-4cbc-bb5f-3d17146dd750</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:07</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:37</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>anon:2680c3ce</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>prj_7f47a9f20bd94002b1f0e429add9e952</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:15</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:45</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>stevenyang.dev@gmail.com</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="n">
+        <v>13.8514</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>3296f689-9bf7-44b2-bb76-171ca01186a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:16</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:46</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>umangshankar10@gmail.com</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="n">
+        <v>3.107</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>31481e39-df1c-4bfc-b2f0-0f9d983d2e14</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:18</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:48</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>44090311-4bd8-4f29-9348-091c7ecb388f</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:19</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:49</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:21</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:51</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:21</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:51</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>kshitijatus@gmail.com</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="n">
+        <v>1.1703</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>fe8b9d27-9f88-4952-bdab-74f6301cb298</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:23</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:53</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>kshitijatus@gmail.com</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>fe8b9d27-9f88-4952-bdab-74f6301cb298</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:28</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:58</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Matthew.you.2520@gmail.com</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="n">
+        <v>3.0374</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>ee265c54-63cd-4a05-90a1-f79c99287fba</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:32</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-07-27 08:02</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>ayaan.chawla@gmail.com</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>258b2fdb-8331-4a4f-8afd-0db2894bc376</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:39</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-07-27 08:09</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>aakashryback@gmail.com</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="n">
+        <v>1.0063</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>61534301-1c76-4ab0-ac67-8e6892249c37</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:42</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-07-27 08:12</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>neil_shah@my.cuesta.edu</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="n">
+        <v>1.9425</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>2964fe6f-019c-491d-9f48-33694692f01e</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:44</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-07-27 08:14</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>walterchen.ca@gmail.com</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="n">
+        <v>0.7677</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>c63e2036-d757-4dcc-bd2f-687ef5b54cc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:44</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-07-27 08:14</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>neil_shah@my.cuesta.edu</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="n">
+        <v>0.1044</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>2964fe6f-019c-491d-9f48-33694692f01e</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-07-27 02:47</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-07-27 08:17</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>neil_shah@my.cuesta.edu</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>metered</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>2964fe6f-019c-491d-9f48-33694692f01e</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12386,7 +15976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12435,10 +16025,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>86.31</v>
+        <v>148.95</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -12449,69 +16039,69 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>prj_b180bd849abe4731b391c1dd585be000</t>
+          <t>3296f689-9bf7-44b2-bb76-171ca01186a3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rafael Lopez</t>
+          <t>stevenyang.dev@gmail.com</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>26.7</v>
+        <v>72.45</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>(blank), claude-opus-4-6, claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
+          <t>prj_b180bd849abe4731b391c1dd585be000</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>toledosean@gmail.com</t>
+          <t>Rafael Lopez</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>19.97</v>
+        <v>35.19</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(blank), claude-opus-4-6, claude-sonnet-4-6</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3296f689-9bf7-44b2-bb76-171ca01186a3</t>
+          <t>prj_9408e7836d3240fcb14fa6ae0caa0453</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>stevenyang.dev@gmail.com</t>
+          <t>toledosean@gmail.com</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>18.62</v>
+        <v>19.97</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>claude-opus-4-6, claude-sonnet-4-6</t>
+          <t>(blank), claude-opus-4-6, claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
@@ -12564,42 +16154,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
+          <t>fe8b9d27-9f88-4952-bdab-74f6301cb298</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sahasrakokkula77@gmail.com</t>
+          <t>kshitijatus@gmail.com</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12.17</v>
+        <v>13.98</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fa325ad8-92a1-460b-bebc-6e41d0744990</t>
+          <t>prj_4a221e53ef884270ad1424fee9f41f90</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>philipnisevich@gmail.com</t>
+          <t>sahasrakokkula77@gmail.com</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>11.76</v>
+        <v>12.17</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -12610,19 +16200,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>prj_4f409ce952ed458ebf2627aa06c44fad</t>
+          <t>fa325ad8-92a1-460b-bebc-6e41d0744990</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>enochfyw@gmail.com</t>
+          <t>philipnisevich@gmail.com</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10.53</v>
+        <v>11.76</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -12633,19 +16223,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
+          <t>prj_4f409ce952ed458ebf2627aa06c44fad</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>justin-kang@berkeley.edu</t>
+          <t>enochfyw@gmail.com</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8.9</v>
+        <v>10.53</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -12656,19 +16246,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>prj_154ea02e80f04b71877b98956e565c12</t>
+          <t>prj_bfde8a2032ee4e6c9ea636a6afcadf2c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kakanisnehil@gmail.com</t>
+          <t>justin-kang@berkeley.edu</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8.279999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -12679,19 +16269,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9f23a6c7-a167-4b13-aa92-58e43f20cb1d</t>
+          <t>prj_154ea02e80f04b71877b98956e565c12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>noriaki@uni.minerva.edu</t>
+          <t>kakanisnehil@gmail.com</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8.1</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -12702,19 +16292,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>prj_d071db4af98d4fe1a789f8c1bb45b0e6</t>
+          <t>9f23a6c7-a167-4b13-aa92-58e43f20cb1d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>umangshankar10@gmail.com</t>
+          <t>noriaki@uni.minerva.edu</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7.43</v>
+        <v>8.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -12725,19 +16315,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>prj_7782ae176a0f4d33bbee7296d3956151</t>
+          <t>prj_d071db4af98d4fe1a789f8c1bb45b0e6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>stepodkelly@gmail.com</t>
+          <t>umangshankar10@gmail.com</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7.38</v>
+        <v>7.43</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -12748,65 +16338,65 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>prj_ce4dd6df91864d219f2baa8910a1d9ea</t>
+          <t>prj_7782ae176a0f4d33bbee7296d3956151</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>toledosean@gmail.com</t>
+          <t>stepodkelly@gmail.com</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7.34</v>
+        <v>7.38</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>730ceb72-ce18-4665-aeb1-94ca18c2a89c</t>
+          <t>prj_ce4dd6df91864d219f2baa8910a1d9ea</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>clai74@mail.ccsf.edu</t>
+          <t>toledosean@gmail.com</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6.08</v>
+        <v>7.34</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>prj_826a6397e8994cdf9b1284c5daf5d5ac</t>
+          <t>prj_36eb9b5db1be4be39f04ac6563777c3c</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>amyhsieh3730@gmail.com</t>
+          <t>anon:2680c3ce</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5.83</v>
+        <v>6.54</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -12817,42 +16407,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>prj_6d60ee35c5824b948b8c4dddff7c74e6</t>
+          <t>730ceb72-ce18-4665-aeb1-94ca18c2a89c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>owin@owinrojas.com</t>
+          <t>clai74@mail.ccsf.edu</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4.82</v>
+        <v>6.08</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>claude-opus-4-6, claude-sonnet-4-6</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fa55ae9f-922d-4eff-ae70-bf6acb005dbb</t>
+          <t>prj_826a6397e8994cdf9b1284c5daf5d5ac</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mborgiottitulane@gmail.com</t>
+          <t>amyhsieh3730@gmail.com</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4.81</v>
+        <v>5.83</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -12863,19 +16453,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>prj_51062113208340d5befa46d932c1d25e</t>
+          <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rosekr1</t>
+          <t>benjinisevich2@gmail.com</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4.49</v>
+        <v>5.37</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -12886,42 +16476,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>prj_e221843d682c48b1a60cff3283d0d81c</t>
+          <t>prj_6d60ee35c5824b948b8c4dddff7c74e6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>kewinszlezingier@gmail.com</t>
+          <t>owin@owinrojas.com</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>4.23</v>
+        <v>4.82</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>claude-opus-4-6, claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>prj_dafde1251b6940458b46b6227142a03f</t>
+          <t>fa55ae9f-922d-4eff-ae70-bf6acb005dbb</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>misha@mypipdev.com</t>
+          <t>mborgiottitulane@gmail.com</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4.2</v>
+        <v>4.81</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -12932,19 +16522,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>prj_794da3117b7b446bb859f76773f4882a</t>
+          <t>prj_51062113208340d5befa46d932c1d25e</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>amberkaurtoor@gmail.com</t>
+          <t>Rosekr1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4.11</v>
+        <v>4.49</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -12955,19 +16545,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prj_715a659716294948bf46a6425577322c</t>
+          <t>prj_e221843d682c48b1a60cff3283d0d81c</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>schan119@calpoly.edu</t>
+          <t>kewinszlezingier@gmail.com</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4.04</v>
+        <v>4.23</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -12978,19 +16568,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>prj_3c602ac0e7c845da83a5c97fa9563637</t>
+          <t>prj_dafde1251b6940458b46b6227142a03f</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yujiwork@outlook.com</t>
+          <t>misha@mypipdev.com</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -13001,19 +16591,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>prj_26b13de9412d40c9976e06c441f7197e</t>
+          <t>prj_c650bb9fe85c46129b6250e1e9103c2e</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nagatarunmoturi@gmail.com</t>
+          <t>anon:2680c3ce</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3.93</v>
+        <v>4.14</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -13024,65 +16614,65 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>prj_c650bb9fe85c46129b6250e1e9103c2e</t>
+          <t>8537287b-c8a9-4cbc-bb5f-3d17146dd750</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>anon:2680c3ce</t>
+          <t>phongct1105@gmail.com</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>3.41</v>
+        <v>4.12</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>(blank), claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>prj_4a420277e75948f8a54a6326131e7ebc</t>
+          <t>prj_794da3117b7b446bb859f76773f4882a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sohamjani8@gmail.com</t>
+          <t>amberkaurtoor@gmail.com</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>3.18</v>
+        <v>4.11</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>gpt-5.4</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>prj_12917802ae254e84b005def4535aeaef</t>
+          <t>prj_715a659716294948bf46a6425577322c</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nagatarunmoturi@gmail.com</t>
+          <t>schan119@calpoly.edu</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2.77</v>
+        <v>4.04</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -13093,42 +16683,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>prj_97639f12bbf345a09ee342fede643ac6</t>
+          <t>prj_3c602ac0e7c845da83a5c97fa9563637</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>owin@owinrojas.com</t>
+          <t>yujiwork@outlook.com</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>b02be0c1-41f9-4b64-bd16-92af548b6460</t>
+          <t>prj_26b13de9412d40c9976e06c441f7197e</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ryanxu240@gmail.com</t>
+          <t>nagatarunmoturi@gmail.com</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2.74</v>
+        <v>3.93</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -13139,42 +16729,42 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>aa8d4bef-a2f4-4f6d-8e63-8f3b68f7ac8e</t>
+          <t>prj_4a420277e75948f8a54a6326131e7ebc</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>benjinisevich2@gmail.com</t>
+          <t>sohamjani8@gmail.com</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>2.71</v>
+        <v>3.18</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>gpt-5.4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cea6e72d-3cf1-4e43-bfa1-3bad217a1f8f</t>
+          <t>52346906-65af-4401-87d9-210a31892a01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>142857tom@gmail.com</t>
+          <t>rishabh.rb@icloud.com</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2.62</v>
+        <v>3.12</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -13185,19 +16775,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>35b02362-40b1-4e47-8bc8-2691f01f8f98</t>
+          <t>31481e39-df1c-4bfc-b2f0-0f9d983d2e14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>benjinisevich2@gmail.com</t>
+          <t>umangshankar10@gmail.com</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2.42</v>
+        <v>3.11</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -13208,65 +16798,65 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>prj_4cb223a06d044e3884571a1a9db05c15</t>
+          <t>6493a4ed-eb46-4283-9b74-c40698d83caa</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>manidweepsharma1801@gmail.com</t>
+          <t>atharavhedage@gmail.com</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6, gpt-5.2</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3a4b96ec-339b-4a92-833f-94048883eb44</t>
+          <t>ee265c54-63cd-4a05-90a1-f79c99287fba</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wanzelin007@gmail.com</t>
+          <t>Matthew.you.2520@gmail.com</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>2.34</v>
+        <v>3.04</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(blank)</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>52346906-65af-4401-87d9-210a31892a01</t>
+          <t>prj_12917802ae254e84b005def4535aeaef</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>rishabh.rb@icloud.com</t>
+          <t>nagatarunmoturi@gmail.com</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -13277,19 +16867,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>prj_1fd2a79470114b5b852f5d14a3508009</t>
+          <t>prj_97639f12bbf345a09ee342fede643ac6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>toledosean@gmail.com</t>
+          <t>owin@owinrojas.com</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -13300,19 +16890,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>prj_36eb9b5db1be4be39f04ac6563777c3c</t>
+          <t>b02be0c1-41f9-4b64-bd16-92af548b6460</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>anon:2680c3ce</t>
+          <t>ryanxu240@gmail.com</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1.55</v>
+        <v>2.74</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -13323,19 +16913,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>e5fccb47-d2f2-4430-97a0-88f20bb10eb7</t>
+          <t>cea6e72d-3cf1-4e43-bfa1-3bad217a1f8f</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>amyhsieh3730@gmail.com</t>
+          <t>142857tom@gmail.com</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.17</v>
+        <v>2.62</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -13346,42 +16936,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fe8b9d27-9f88-4952-bdab-74f6301cb298</t>
+          <t>8c32b563-ccaa-4bb0-8ffa-b135bbf688d1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>kshitijatus@gmail.com</t>
+          <t>arshmeetsodhi@gmail.com</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1.12</v>
+        <v>2.47</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>prj_d320c0b34bd54ff0b5cf05e31219765c</t>
+          <t>35b02362-40b1-4e47-8bc8-2691f01f8f98</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>tiwari.aadi123@gmail.com</t>
+          <t>benjinisevich2@gmail.com</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.86</v>
+        <v>2.42</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -13392,111 +16982,111 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>prj_3dfb58dc3ca8426e942cc2306d8b7b85</t>
+          <t>prj_4cb223a06d044e3884571a1a9db05c15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>likhith11ramesh@gmail.com</t>
+          <t>manidweepsharma1801@gmail.com</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.68</v>
+        <v>2.38</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>claude-opus-4-5-20251101, gpt-5.2</t>
+          <t>claude-sonnet-4-6, gpt-5.2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>prj_465443b9ab494e4b9cfc467954362ac0</t>
+          <t>3a4b96ec-339b-4a92-833f-94048883eb44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ryanandnoahlee@gmail.com</t>
+          <t>wanzelin007@gmail.com</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.24</v>
+        <v>2.34</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>(blank)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>prj_f66b714e163345618972deabd55a5407</t>
+          <t>2964fe6f-019c-491d-9f48-33694692f01e</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>toledosean@gmail.com</t>
+          <t>neil_shah@my.cuesta.edu</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.19</v>
+        <v>2.32</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-sonnet-4-6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>prj_e0a8e92dbfa14efebfe76d073967ae58</t>
+          <t>prj_1fd2a79470114b5b852f5d14a3508009</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>sahilnale@icloud.com</t>
+          <t>toledosean@gmail.com</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.18</v>
+        <v>2.16</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>prj_51a8b847823248a093dcdbf1067a9a6b</t>
+          <t>prj_7f47a9f20bd94002b1f0e429add9e952</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>aneeshpradhan@acm.org</t>
+          <t>anon:2680c3ce</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.12</v>
+        <v>2.16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -13507,42 +17097,42 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>63389cd5-92cf-45f5-b3eb-325d934e47bb</t>
+          <t>d0698e37-e8f0-4255-83a3-02c9c3538473</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>harshjannawar14@gmail.com</t>
+          <t>praniil.nagaraj@gmail.com</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.11</v>
+        <v>1.67</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>30ca70e5-76b0-491c-bf8b-98bebafb3efd</t>
+          <t>dccc4223-c2a9-4dea-8f36-9499b046eef6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>chengreric@gmail.com</t>
+          <t>fkw155@mun.ca</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.11</v>
+        <v>1.32</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -13553,42 +17143,42 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>34dbf079-fc90-41f4-968e-036f650caa81</t>
+          <t>8a3b0c74-939b-41ee-bd4b-7ed78557ab9d</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>benjinisevich2@gmail.com</t>
+          <t>anon:23f87ab2</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.09</v>
+        <v>1.28</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>(blank)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>prj_d2953e5b401b46e7bbb69676b77c602a</t>
+          <t>e5fccb47-d2f2-4430-97a0-88f20bb10eb7</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>cajuliawan@gmail.com</t>
+          <t>amyhsieh3730@gmail.com</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -13599,19 +17189,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>prj_55c6fa88a091493592ad068707740160</t>
+          <t>prj_e0a8e92dbfa14efebfe76d073967ae58</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>cajuliawan@gmail.com</t>
+          <t>sahilnale@icloud.com</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.06</v>
+        <v>1.11</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -13622,19 +17212,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>240f17e1-96dc-45eb-86f8-9032fa60ce02</t>
+          <t>61534301-1c76-4ab0-ac67-8e6892249c37</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>samrocksnature@gmail.com</t>
+          <t>aakashryback@gmail.com</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.06</v>
+        <v>1.01</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -13645,19 +17235,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>c1e560cb-557a-4a72-abad-e5b7476b8810</t>
+          <t>prj_d320c0b34bd54ff0b5cf05e31219765c</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>lee.anastasia.y@gmail.com</t>
+          <t>tiwari.aadi123@gmail.com</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.04</v>
+        <v>0.86</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -13668,19 +17258,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>prj_8b6bccf2526f4b59aa02df3d39b1bc76</t>
+          <t>c63e2036-d757-4dcc-bd2f-687ef5b54cc5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>manidweepsharma1801@gmail.com</t>
+          <t>walterchen.ca@gmail.com</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.03</v>
+        <v>0.77</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -13691,44 +17281,412 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>prj_3f1220f275a5465f91ddb4c885d651ac</t>
+          <t>prj_3dfb58dc3ca8426e942cc2306d8b7b85</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>mp@gmail.com</t>
+          <t>likhith11ramesh@gmail.com</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.03</v>
+        <v>0.68</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>claude-sonnet-4-6</t>
+          <t>claude-opus-4-5-20251101, gpt-5.2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>prj_4620f251f9ab4774b9aa1a1d2f70b200</t>
+          <t>f84bedd1-4803-4190-b89c-c72f7deffdfe</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>toledosean@gmail.com</t>
+          <t>samrocksnature@gmail.com</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>prj_465443b9ab494e4b9cfc467954362ac0</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ryanandnoahlee@gmail.com</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>prj_f66b714e163345618972deabd55a5407</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>toledosean@gmail.com</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>prj_51a8b847823248a093dcdbf1067a9a6b</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>aneeshpradhan@acm.org</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>63389cd5-92cf-45f5-b3eb-325d934e47bb</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>harshjannawar14@gmail.com</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>30ca70e5-76b0-491c-bf8b-98bebafb3efd</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>chengreric@gmail.com</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>34dbf079-fc90-41f4-968e-036f650caa81</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>6ea9e44e-bc7f-465b-94a6-5044f8507a6f</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>jczhang223@gmail.com</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>prj_d2953e5b401b46e7bbb69676b77c602a</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>cajuliawan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>47d22643-2cf7-4828-88f5-be4eb756755f</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>visheshv05@gmail.com</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>prj_55c6fa88a091493592ad068707740160</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>cajuliawan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>240f17e1-96dc-45eb-86f8-9032fa60ce02</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>samrocksnature@gmail.com</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>c1e560cb-557a-4a72-abad-e5b7476b8810</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>lee.anastasia.y@gmail.com</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>prj_8b6bccf2526f4b59aa02df3d39b1bc76</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>manidweepsharma1801@gmail.com</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>prj_3f1220f275a5465f91ddb4c885d651ac</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>mp@gmail.com</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>prj_4620f251f9ab4774b9aa1a1d2f70b200</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>toledosean@gmail.com</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>claude-sonnet-4-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>258b2fdb-8331-4a4f-8afd-0db2894bc376</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ayaan.chawla@gmail.com</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>claude-sonnet-4-6</t>
         </is>
@@ -13795,16 +17753,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>219.17</v>
+        <v>260</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.2313</v>
+        <v>1.1872</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>9.02</v>
@@ -13817,16 +17775,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>123.99</v>
+        <v>234.99</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3.0242</v>
+        <v>3.4557</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>25.98</v>
@@ -13839,19 +17797,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4.34</v>
+        <v>27.38</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.1694</v>
+        <v>5.4757</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2.34</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="5">
